--- a/144/DQ Templates and Instructions/Topic 2 DQ 2/Topic 2 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 2 DQ 2/Topic 2 DQ 2.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 2 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{04F808BF-0000-4781-8875-81665D9480C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8E5A105-58BF-4673-AD55-E26430D30BFA}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{04F808BF-0000-4781-8875-81665D9480C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84DB3DF3-FCC0-42BE-880C-3D8A74216449}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F5830A4-E866-4CA9-84DB-696DC6FA58AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="5" r:id="rId1"/>
     <sheet name="Inflation Rate &amp; Projection" sheetId="1" r:id="rId2"/>
-    <sheet name="solution" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="CPI" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Random" sheetId="2" state="hidden" r:id="rId5"/>
-    <sheet name="Halo" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Users" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="solution" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="CPI" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="Random" sheetId="2" state="hidden" r:id="rId6"/>
+    <sheet name="Halo" sheetId="6" state="hidden" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="84">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -338,6 +339,12 @@
   <si>
     <t>Download the Excel to complete the template.</t>
   </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
 </sst>
 </file>
 
@@ -347,7 +354,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,12 +426,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -867,7 +868,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1150,6 +1151,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
@@ -1262,11 +1269,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2171,10 +2179,10 @@
       <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="C3" s="125" t="s">
+      <c r="C3" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="126"/>
+      <c r="D3" s="92"/>
     </row>
     <row r="4" spans="2:13" ht="14.45" customHeight="1" thickTop="1">
       <c r="B4" s="75" t="s">
@@ -2278,12 +2286,12 @@
       <c r="I11" s="41">
         <v>15</v>
       </c>
-      <c r="J11" s="91" t="s">
+      <c r="J11" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="92"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="94"/>
     </row>
     <row r="12" spans="2:13" ht="14.45" customHeight="1">
       <c r="B12" s="78"/>
@@ -2295,12 +2303,12 @@
       <c r="I12" s="42">
         <v>15</v>
       </c>
-      <c r="J12" s="93" t="s">
+      <c r="J12" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="94"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="96"/>
     </row>
     <row r="13" spans="2:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="B13" s="81"/>
@@ -2312,12 +2320,12 @@
       <c r="I13" s="43">
         <v>16</v>
       </c>
-      <c r="J13" s="95" t="s">
+      <c r="J13" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="95"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="96"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="98"/>
     </row>
     <row r="14" spans="2:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="B14" s="13"/>
@@ -2329,12 +2337,12 @@
       <c r="I14" s="44">
         <v>16</v>
       </c>
-      <c r="J14" s="97" t="s">
+      <c r="J14" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="97"/>
-      <c r="L14" s="97"/>
-      <c r="M14" s="98"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="99"/>
+      <c r="M14" s="100"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="15" t="str">
@@ -2476,6 +2484,172 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022204A5-B628-40B4-A45C-FE89C5667B75}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="127">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>'Inflation Rate &amp; Projection'!C2</f>
+        <v>Your Name Here</v>
+      </c>
+      <c r="F1" s="128" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="14" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="14" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="14" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="14" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="cwa0bQVEVr4ROFxzwvzmrkObM+LrgKK+LKSM33+B9yy64W8tZpIZxypX7OUFg01IiWTYTR2zoDwS02NCSORqkw==" saltValue="MytS9r3fly/BA0xpl8OJ3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D03631F-4AA9-4151-A134-C642E1B2C8F1}">
   <dimension ref="B1:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2496,11 +2670,11 @@
       <c r="B2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="99" t="str">
+      <c r="C2" s="101" t="str">
         <f>'Inflation Rate &amp; Projection'!C2</f>
         <v>Your Name Here</v>
       </c>
-      <c r="D2" s="100"/>
+      <c r="D2" s="102"/>
       <c r="E2" s="51" t="s">
         <v>8</v>
       </c>
@@ -2509,26 +2683,26 @@
     </row>
     <row r="3" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:10" ht="14.45" customHeight="1" thickTop="1">
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="103"/>
-      <c r="I4" s="110" t="s">
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="105"/>
+      <c r="I4" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="111"/>
+      <c r="J4" s="113"/>
     </row>
     <row r="5" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B5" s="104"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108"/>
       <c r="I5" s="53" t="s">
         <v>12</v>
       </c>
@@ -2537,12 +2711,12 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B6" s="104"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="106"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="108"/>
       <c r="I6" s="53" t="s">
         <v>14</v>
       </c>
@@ -2551,12 +2725,12 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B7" s="104"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="106"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="108"/>
       <c r="I7" s="53" t="s">
         <v>16</v>
       </c>
@@ -2565,12 +2739,12 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B8" s="104"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="108"/>
       <c r="I8" s="53" t="s">
         <v>18</v>
       </c>
@@ -2579,12 +2753,12 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B9" s="104"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="106"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="108"/>
       <c r="I9" s="55" t="s">
         <v>20</v>
       </c>
@@ -2593,36 +2767,36 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="14.45" customHeight="1" thickTop="1">
-      <c r="B10" s="104"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="108"/>
     </row>
     <row r="11" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B11" s="104"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="106"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="108"/>
     </row>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="104"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="106"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
     </row>
     <row r="13" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="109"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
     </row>
     <row r="14" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
       <c r="B14" s="57"/>
@@ -2694,19 +2868,19 @@
     </row>
     <row r="18" spans="2:7" ht="27" thickBot="1">
       <c r="B18" s="65"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
     </row>
     <row r="19" spans="2:7" ht="72" customHeight="1" thickBot="1">
-      <c r="B19" s="113" t="str">
+      <c r="B19" s="115" t="str">
         <f>IF($C$2="Your Name Here","Enter Your Name in C2","Part 2: Based on the Inflation Rates, if you made $"&amp;Random!H22&amp;"/hour in "&amp;Random!H23&amp;" "&amp;Random!H26&amp;", how much should you make in "&amp;Random!H23&amp;" "&amp;Random!H28&amp;" to keep up with inflation? How much money would that be a week if you worked 40 hours a week?"&amp;"
 Format all cells as Currency with 2 decimal places.")</f>
         <v>Enter Your Name in C2</v>
       </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="117"/>
     </row>
     <row r="20" spans="2:7" ht="27.95" customHeight="1" thickBot="1">
       <c r="B20" s="66" t="s">
@@ -2773,7 +2947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0212CEF0-2D2C-4D1A-885C-B0174BA7270B}">
   <dimension ref="A3:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3344,7 +3518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40320ECC-5516-4253-AC02-CA304AF310BF}">
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4940,103 +5114,103 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C158F2-D174-413A-9F2B-486C42FCAD67}">
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:9">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="118"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="120"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="119"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="123"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="119"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="121"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="123"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="121"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="123"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="119"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="121"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="123"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="119"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="121"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="123"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="119"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="121"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
+      <c r="I8" s="123"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="119"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="121"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="123"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B10" s="122"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="123"/>
-      <c r="H10" s="123"/>
-      <c r="I10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5047,15 +5221,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5272,6 +5437,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5283,14 +5457,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454AD3E4-F790-402D-B12B-9C20629F0D77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECBA3FAA-2FAC-4519-A31B-04A52D17B51F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5309,6 +5475,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454AD3E4-F790-402D-B12B-9C20629F0D77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40BAD010-3473-43F1-A94E-36D2C645882C}">
   <ds:schemaRefs>
